--- a/pesaje/analytica/Report/ActaEntrega-Export-Base.xlsx
+++ b/pesaje/analytica/Report/ActaEntrega-Export-Base.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\pesaje\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E6CCD1-6A7D-4614-8FBA-9AB092830526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4CC465-8FEB-4AB0-BC1E-7C29D65C8667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Analytica Mineral Services Sac</t>
   </si>
@@ -39,76 +39,46 @@
     <t>Exportado por:</t>
   </si>
   <si>
-    <t>LOTE</t>
-  </si>
-  <si>
-    <t>FECHA PESADO</t>
+    <t>Nª ACTA</t>
   </si>
   <si>
     <t>PROVEEDOR</t>
   </si>
   <si>
-    <t>PLACA</t>
+    <t>CONCESION</t>
   </si>
   <si>
     <t>SUCURSAL</t>
   </si>
   <si>
+    <t>FECHA ENTREGA</t>
+  </si>
+  <si>
+    <t>HORA ENTREGA</t>
+  </si>
+  <si>
+    <t>CODIGO</t>
+  </si>
+  <si>
+    <t>TMH</t>
+  </si>
+  <si>
+    <t>NRO LOTES</t>
+  </si>
+  <si>
+    <t>TOTAL LOTES</t>
+  </si>
+  <si>
+    <t>TOTAL TICKETS</t>
+  </si>
+  <si>
+    <t>DIFERENCIA</t>
+  </si>
+  <si>
+    <t>ESTADO</t>
+  </si>
+  <si>
     <t>,</t>
-  </si>
-  <si>
-    <t>PROCEDENCIA</t>
-  </si>
-  <si>
-    <t>RUC</t>
-  </si>
-  <si>
-    <t>FECHA INGRESO</t>
-  </si>
-  <si>
-    <t>TIPO MINERAL</t>
-  </si>
-  <si>
-    <t>SACOS</t>
-  </si>
-  <si>
-    <t>TMH</t>
-  </si>
-  <si>
-    <t>ESTADO</t>
-  </si>
-  <si>
-    <t>NRO TICKET</t>
-  </si>
-  <si>
-    <t>GRR</t>
-  </si>
-  <si>
-    <t>GRT</t>
-  </si>
-  <si>
-    <t>TRANSPORTISTA</t>
-  </si>
-  <si>
-    <t>FECHA SALIDA</t>
-  </si>
-  <si>
-    <t>CONDUCTOR</t>
-  </si>
-  <si>
-    <t>PESO BRUTO</t>
-  </si>
-  <si>
-    <t>PESO TARA</t>
-  </si>
-  <si>
-    <t>PESO NETO</t>
-  </si>
-  <si>
-    <t>ENVASE</t>
-  </si>
-  <si>
-    <t>SACOS SEGÚN MINERO</t>
   </si>
 </sst>
 </file>
@@ -119,7 +89,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;S/ &quot;* #,##0.00_-;&quot;-S/ &quot;* #,##0.00_-;_-&quot;S/ &quot;* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,15 +126,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -176,12 +146,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -248,47 +212,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="24">
@@ -574,36 +532,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="28.44140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="25.77734375" style="4" customWidth="1"/>
-    <col min="8" max="9" width="28.5546875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="24.77734375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="14.88671875" style="4" customWidth="1"/>
-    <col min="12" max="24" width="24.6640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="53.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="23.88671875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="25.77734375" style="3" customWidth="1"/>
+    <col min="9" max="10" width="28.5546875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24.77734375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="24.6640625" style="3" customWidth="1"/>
+    <col min="16374" max="16384" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
@@ -615,48 +575,37 @@
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
-    </row>
-    <row r="2" spans="1:49" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+    </row>
+    <row r="2" spans="1:50" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="4"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
@@ -668,48 +617,37 @@
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
-      <c r="AM2" s="1"/>
-      <c r="AN2" s="1"/>
-      <c r="AO2" s="1"/>
-      <c r="AP2" s="1"/>
-      <c r="AQ2" s="1"/>
-      <c r="AR2" s="1"/>
-      <c r="AS2" s="1"/>
-      <c r="AT2" s="1"/>
-      <c r="AU2" s="1"/>
-      <c r="AV2" s="1"/>
-      <c r="AW2" s="1"/>
-    </row>
-    <row r="3" spans="1:49" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+    </row>
+    <row r="3" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="4"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -721,33 +659,22 @@
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-      <c r="AH3" s="1"/>
-      <c r="AI3" s="1"/>
-      <c r="AJ3" s="1"/>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="1"/>
-      <c r="AM3" s="1"/>
-      <c r="AN3" s="1"/>
-      <c r="AO3" s="1"/>
-      <c r="AP3" s="1"/>
-      <c r="AQ3" s="1"/>
-      <c r="AR3" s="1"/>
-      <c r="AS3" s="1"/>
-      <c r="AT3" s="1"/>
-      <c r="AU3" s="1"/>
-      <c r="AV3" s="1"/>
-      <c r="AW3" s="1"/>
-    </row>
-    <row r="4" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+    </row>
+    <row r="4" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -759,8 +686,8 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="4"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
@@ -772,33 +699,22 @@
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="1"/>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="1"/>
-      <c r="AR4" s="1"/>
-      <c r="AS4" s="1"/>
-      <c r="AT4" s="1"/>
-      <c r="AU4" s="1"/>
-      <c r="AV4" s="1"/>
-      <c r="AW4" s="1"/>
-    </row>
-    <row r="5" spans="1:49" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+    </row>
+    <row r="5" spans="1:50" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -810,21 +726,23 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
-    </row>
-    <row r="6" spans="1:49" ht="18" x14ac:dyDescent="0.3">
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="1:50" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="9"/>
+      <c r="H6" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:50" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -836,93 +754,86 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
-    </row>
-    <row r="8" spans="1:49" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="H8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="I8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
+      <c r="AS8"/>
+      <c r="AT8"/>
+      <c r="AU8"/>
+      <c r="AV8"/>
+      <c r="AW8"/>
+      <c r="AX8"/>
+    </row>
+    <row r="9" spans="1:50" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AM9"/>
+      <c r="AN9"/>
+      <c r="AO9"/>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+      <c r="AR9"/>
+      <c r="AS9"/>
+      <c r="AT9"/>
+      <c r="AU9"/>
+      <c r="AV9"/>
+      <c r="AW9"/>
+      <c r="AX9"/>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="G11" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:49" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.3">
-      <c r="F11" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/pesaje/analytica/Report/ActaEntrega-Export-Base.xlsx
+++ b/pesaje/analytica/Report/ActaEntrega-Export-Base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\pesaje\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4CC465-8FEB-4AB0-BC1E-7C29D65C8667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963D2AA9-7404-4250-B4E6-149B8CAEFE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Analytica Mineral Services Sac</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>,</t>
+  </si>
+  <si>
+    <t>GUARDIA</t>
+  </si>
+  <si>
+    <t>TURNO</t>
   </si>
 </sst>
 </file>
@@ -214,12 +220,6 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -247,6 +247,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="24">
@@ -532,272 +538,291 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="53.77734375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="42.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.88671875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="28.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="25.77734375" style="3" customWidth="1"/>
-    <col min="9" max="10" width="28.5546875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="24.77734375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="24.6640625" style="3" customWidth="1"/>
-    <col min="16374" max="16384" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="53.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="42.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="23.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="65.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="28.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24.6640625" style="1" customWidth="1"/>
+    <col min="16376" max="16384" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-      <c r="AK1" s="5"/>
-      <c r="AL1" s="5"/>
-    </row>
-    <row r="2" spans="1:50" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+    </row>
+    <row r="2" spans="1:52" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-    </row>
-    <row r="3" spans="1:50" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+    </row>
+    <row r="3" spans="1:52" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="4"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
       <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="5"/>
-      <c r="AJ3" s="5"/>
-      <c r="AK3" s="5"/>
-      <c r="AL3" s="5"/>
-    </row>
-    <row r="4" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3"/>
+      <c r="AN3" s="3"/>
+    </row>
+    <row r="4" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="5"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
-      <c r="AL4" s="5"/>
-    </row>
-    <row r="5" spans="1:50" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:50" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10" t="s">
+      <c r="N4" s="4"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3"/>
+    </row>
+    <row r="5" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:52" ht="18" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="1:50" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    <row r="7" spans="1:52" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="I8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="J8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="K8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="L8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="M8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="N8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="O8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AM8"/>
-      <c r="AN8"/>
       <c r="AO8"/>
       <c r="AP8"/>
       <c r="AQ8"/>
@@ -808,10 +833,10 @@
       <c r="AV8"/>
       <c r="AW8"/>
       <c r="AX8"/>
-    </row>
-    <row r="9" spans="1:50" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="AM9"/>
-      <c r="AN9"/>
+      <c r="AY8"/>
+      <c r="AZ8"/>
+    </row>
+    <row r="9" spans="1:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="AO9"/>
       <c r="AP9"/>
       <c r="AQ9"/>
@@ -822,16 +847,18 @@
       <c r="AV9"/>
       <c r="AW9"/>
       <c r="AX9"/>
-    </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="G11" s="3" t="s">
+      <c r="AY9"/>
+      <c r="AZ9"/>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="I11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/pesaje/analytica/Report/ActaEntrega-Export-Base.xlsx
+++ b/pesaje/analytica/Report/ActaEntrega-Export-Base.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\pesaje\analytica\Report\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963D2AA9-7404-4250-B4E6-149B8CAEFE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -27,81 +22,97 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>Analytica Mineral Services Sac</t>
-  </si>
-  <si>
-    <t>Av. Javier Prado Este Nro. 4019</t>
-  </si>
-  <si>
-    <t>Fecha reporte:</t>
-  </si>
-  <si>
-    <t>Exportado por:</t>
-  </si>
-  <si>
-    <t>Nª ACTA</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>CONCESION</t>
-  </si>
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>FECHA ENTREGA</t>
-  </si>
-  <si>
-    <t>HORA ENTREGA</t>
-  </si>
-  <si>
-    <t>CODIGO</t>
-  </si>
-  <si>
-    <t>TMH</t>
-  </si>
-  <si>
-    <t>NRO LOTES</t>
-  </si>
-  <si>
-    <t>TOTAL LOTES</t>
-  </si>
-  <si>
-    <t>TOTAL TICKETS</t>
-  </si>
-  <si>
-    <t>DIFERENCIA</t>
-  </si>
-  <si>
-    <t>ESTADO</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>GUARDIA</t>
-  </si>
-  <si>
-    <t>TURNO</t>
+    <t xml:space="preserve">Analytica Mineral Services Sac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Av. Javier Prado Este Nro. 4019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha reporte:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exportado por:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nª ACTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROVEEDOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCESION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUCURSAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECHA ENTREGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HORA ENTREGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CODIGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRO LOTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL LOTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL TICKETS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIFERENCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">,</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;S/ &quot;* #,##0.00_-;&quot;-S/ &quot;* #,##0.00_-;_-&quot;S/ &quot;* \-??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;S/ &quot;* #,##0.00_-;&quot;-S/ &quot;* #,##0.00_-;_-&quot;S/ &quot;* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -117,7 +128,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -139,15 +150,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -163,126 +167,208 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+  <cellStyleXfs count="43">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="41" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="41" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="41" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="41" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="41" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="41" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="24">
-    <cellStyle name="Millares 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Millares 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Millares 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Millares 2 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Millares 2 4" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Millares 3" xfId="6" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Millares 3 2" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Millares 3 2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Millares 3 3" xfId="9" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Millares 3 4" xfId="10" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Millares 4" xfId="11" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Millares 4 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Millares 4 2 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Millares 4 3" xfId="14" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Millares 4 4" xfId="15" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Millares 5" xfId="16" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Millares 5 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="Millares 6" xfId="18" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="Millares 7" xfId="19" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="Millares 8" xfId="20" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="Moneda 2" xfId="21" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+  <cellStyles count="29">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="22" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="Normal 3" xfId="23" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Millares 2" xfId="20"/>
+    <cellStyle name="Millares 2 2" xfId="21"/>
+    <cellStyle name="Millares 2 2 2" xfId="22"/>
+    <cellStyle name="Millares 2 3" xfId="23"/>
+    <cellStyle name="Millares 2 4" xfId="24"/>
+    <cellStyle name="Millares 3" xfId="25"/>
+    <cellStyle name="Millares 3 2" xfId="26"/>
+    <cellStyle name="Millares 3 2 2" xfId="27"/>
+    <cellStyle name="Millares 3 3" xfId="28"/>
+    <cellStyle name="Millares 3 4" xfId="29"/>
+    <cellStyle name="Millares 4" xfId="30"/>
+    <cellStyle name="Millares 4 2" xfId="31"/>
+    <cellStyle name="Millares 4 2 2" xfId="32"/>
+    <cellStyle name="Millares 4 3" xfId="33"/>
+    <cellStyle name="Millares 4 4" xfId="34"/>
+    <cellStyle name="Millares 5" xfId="35"/>
+    <cellStyle name="Millares 5 2" xfId="36"/>
+    <cellStyle name="Millares 6" xfId="37"/>
+    <cellStyle name="Millares 7" xfId="38"/>
+    <cellStyle name="Millares 8" xfId="39"/>
+    <cellStyle name="Moneda 2" xfId="40"/>
+    <cellStyle name="Normal 2" xfId="41"/>
+    <cellStyle name="Normal 3" xfId="42"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -341,76 +427,60 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 2013 - Tema de 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -442,7 +512,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -466,7 +536,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -526,38 +596,39 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AN11"/>
+  <sheetFormatPr defaultColWidth="10.66796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="53.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="42.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="50.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" style="1" customWidth="1"/>
-    <col min="6" max="8" width="23.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="25.77734375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="65.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="28.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.77734375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="24.6640625" style="1" customWidth="1"/>
-    <col min="16376" max="16384" width="11.5546875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="53.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="50.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="23.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="28.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="25.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="65.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="28.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="24.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="24.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16376" style="0" width="11.56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -599,23 +670,23 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:52" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="5"/>
       <c r="O2" s="2"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -643,23 +714,23 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="3" spans="1:52" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="3" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="7"/>
       <c r="O3" s="2"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
@@ -687,21 +758,21 @@
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
     </row>
-    <row r="4" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
       <c r="O4" s="2"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
@@ -729,130 +800,105 @@
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
     </row>
-    <row r="5" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
     </row>
-    <row r="6" spans="1:52" ht="18" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
+    <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="18" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+    <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
     </row>
-    <row r="8" spans="1:52" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+    <row r="8" s="12" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="9" t="s">
+    </row>
+    <row r="9" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I11" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="O8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO8"/>
-      <c r="AP8"/>
-      <c r="AQ8"/>
-      <c r="AR8"/>
-      <c r="AS8"/>
-      <c r="AT8"/>
-      <c r="AU8"/>
-      <c r="AV8"/>
-      <c r="AW8"/>
-      <c r="AX8"/>
-      <c r="AY8"/>
-      <c r="AZ8"/>
-    </row>
-    <row r="9" spans="1:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="AO9"/>
-      <c r="AP9"/>
-      <c r="AQ9"/>
-      <c r="AR9"/>
-      <c r="AS9"/>
-      <c r="AT9"/>
-      <c r="AU9"/>
-      <c r="AV9"/>
-      <c r="AW9"/>
-      <c r="AX9"/>
-      <c r="AY9"/>
-      <c r="AZ9"/>
-    </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="I11" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +906,12 @@
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:M3"/>
   </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>